--- a/reports/kelip_bank_kpi_pack.xlsx
+++ b/reports/kelip_bank_kpi_pack.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trend" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly KPIs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI data" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI catalog" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scorecard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Trend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Checks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="KPI data" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Plan" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="KPI catalog" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="report_month">'Scorecard'!$D$5</definedName>
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <lineChart>
@@ -458,7 +458,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575">
+            <a:ln w="28575">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -468,7 +468,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -494,7 +494,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="898781"/>
               </a:solidFill>
@@ -504,7 +504,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -546,7 +546,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="E1E0D9"/>
               </a:solidFill>
@@ -615,7 +615,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -630,9 +630,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/reports/kelip_bank_kpi_pack.xlsx
+++ b/reports/kelip_bank_kpi_pack.xlsx
@@ -25633,7 +25633,7 @@
       </c>
       <c r="O7" s="71" t="inlineStr">
         <is>
-          <t>Growth;Engagement</t>
+          <t>Growth</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="O23" s="71" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Executive;Deposits</t>
         </is>
       </c>
     </row>
